--- a/results/reliability_eval/Llama-3-8B_P127_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P127_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5985717364237142</v>
+        <v>0.6314911259192167</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8352552992086476</v>
+        <v>0.8242010300067606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5985717364237142</v>
+        <v>0.6314911259192167</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8352552992086476</v>
+        <v>0.8242010300067606</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4122539747150656</v>
+        <v>0.3651231373056436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7516738695457575</v>
+        <v>0.6986430310523642</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9983358873671104</v>
+        <v>0.9930883526341895</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9993354144140029</v>
+        <v>0.9970809320573533</v>
       </c>
       <c r="I2" t="n">
-        <v>0.788</v>
+        <v>0.754</v>
       </c>
     </row>
   </sheetData>
